--- a/output/pdf_financials_xlsx/EXE.xlsx
+++ b/output/pdf_financials_xlsx/EXE.xlsx
@@ -34528,7 +34528,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -35734,7 +35734,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -36332,7 +36332,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -37112,7 +37112,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -37870,7 +37870,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -39158,7 +39158,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -39674,7 +39674,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -40626,7 +40626,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -47304,7 +47304,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -47480,7 +47480,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -49196,7 +49196,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -49614,7 +49614,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -51182,7 +51182,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -52226,7 +52226,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -54118,7 +54118,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -57694,7 +57694,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -61010,7 +61010,7 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -63126,7 +63126,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -63558,7 +63558,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -65112,7 +65112,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E692" s="5" t="n">
@@ -65540,7 +65540,7 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E697" s="5" t="n">

--- a/output/pdf_financials_xlsx/EXE.xlsx
+++ b/output/pdf_financials_xlsx/EXE.xlsx
@@ -988,46 +988,46 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>-82.944</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-60.323</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-30.396</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-30.95</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-15.768</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-18.915</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-23.654</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-26.454</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-24.881</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-20.754</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-16.438</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-30.986</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-31.47</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-28.844</v>
       </c>
     </row>
     <row r="14">
@@ -1814,46 +1814,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-32.779</v>
+        <v>50.165</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>29.807</v>
+        <v>90.13</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9.025</v>
+        <v>39.421</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>12.487</v>
+        <v>43.437</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>37.55</v>
+        <v>53.318</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>38.828</v>
+        <v>57.743</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>42.564</v>
+        <v>66.218</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>12.319</v>
+        <v>38.773</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>24.236</v>
+        <v>49.117</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>13.985</v>
+        <v>34.739</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.496</v>
+        <v>11.942</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>44.803</v>
+        <v>75.789</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>99.861</v>
+        <v>131.331</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>130.103</v>
+        <v>158.947</v>
       </c>
     </row>
     <row r="28">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>43.798</v>
+        <v>126.742</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>106.612</v>
+        <v>166.935</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3.316</v>
@@ -1924,34 +1924,34 @@
         <v>19.707</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>61.218</v>
+        <v>76.986</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>70.00700000000001</v>
+        <v>88.922</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>73.943</v>
+        <v>97.59699999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>47.589</v>
+        <v>74.04300000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>63.826</v>
+        <v>88.70699999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>44.816</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>27.063</v>
+        <v>43.501</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>77.02800000000001</v>
+        <v>108.014</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>133.197</v>
+        <v>164.667</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>167.046</v>
+        <v>195.89</v>
       </c>
     </row>
     <row r="30">
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.091513130813407</v>
+        <v>6.052389543484925</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5.232714231233432</v>
+        <v>8.193478690869254</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>44.59386767079075</v>
@@ -1973,34 +1973,34 @@
         <v>2.414721382543477</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>6.489914436767913</v>
+        <v>8.161530151736656</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>6.59971454375079</v>
+        <v>8.382873379225044</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>6.738440816854714</v>
+        <v>8.89403470785023</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>16.47858500725433</v>
+        <v>25.63877933329409</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>23041.87725631769</v>
+        <v>32024.18772563177</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>3.840316987250072</v>
+        <v>5.618742968002214</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>2.215414992260005</v>
+        <v>3.561052639334238</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>5.902723231493452</v>
+        <v>8.277207601476523</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9.084491768528483</v>
+        <v>11.23085359316111</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>10.0605393373195</v>
+        <v>11.7977027333041</v>
       </c>
     </row>
     <row r="31">
@@ -35042,7 +35042,11 @@
           <t>Net finance costs 18</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -36158,7 +36162,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -36678,7 +36686,11 @@
           <t>Net finance costs 17</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -37536,7 +37548,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -38378,7 +38394,11 @@
           <t>Net finance costs 18</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -39932,7 +39952,11 @@
           <t>Net finance costs 16</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -47818,7 +47842,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -50022,7 +50050,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -54540,7 +54572,11 @@
           <t>Net finance costs 6,863 300 7,163 7,845 242</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E568" t="inlineStr">
         <is>
           <t>-</t>
@@ -55636,7 +55672,11 @@
           <t>Net finance costs 6,863 300 7,163 7,845 242</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr">
         <is>
           <t>-</t>
@@ -58116,7 +58156,11 @@
           <t>Net finance costs 29,786 1,164 30,950 28,684 972</t>
         </is>
       </c>
-      <c r="D610" t="inlineStr"/>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E610" t="inlineStr">
         <is>
           <t>-</t>
@@ -59212,7 +59256,11 @@
           <t>Net finance costs 29,786 1,164 30,950 28,684 972</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
           <t>-</t>
@@ -61690,7 +61738,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E652" t="inlineStr">
         <is>
           <t>-</t>
@@ -64236,7 +64288,11 @@
           <t>Net finance costs 21</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E682" t="inlineStr">
         <is>
           <t>-</t>
@@ -66392,7 +66448,11 @@
           <t>Net finance costs 18</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E707" s="5" t="n">
         <v>82.944</v>
       </c>

--- a/output/pdf_financials_xlsx/EXE.xlsx
+++ b/output/pdf_financials_xlsx/EXE.xlsx
@@ -1540,10 +1540,10 @@
         <v>0.00074</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6e-05</v>
+        <v>5.283</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-30.95</v>
+        <v>-18.753</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>232.078</v>
@@ -2065,10 +2065,10 @@
         <v>3.632056927093329e-05</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.0008068854222700376</v>
+        <v>71.04626143087681</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-3.792339107409581</v>
+        <v>-2.297826664983905</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>24.60332520919049</v>
@@ -2409,46 +2409,46 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>23472</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>29438</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>30.863</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>12615</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>11463</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>10.817</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>9.025</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>10.676</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>4.035</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>2.556</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>1.353</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>3.431</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>4.829</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="41">
@@ -2458,46 +2458,46 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>222.707</v>
+        <v>23694.707</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>209.518</v>
+        <v>29647.518</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>210.795</v>
+        <v>241.658</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>36.775</v>
+        <v>12651.775</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>52.678</v>
+        <v>11515.678</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>52.234</v>
+        <v>63.051</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>42.491</v>
+        <v>51.516</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>50.57</v>
+        <v>61.246</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>50.382</v>
+        <v>54.417</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>69.435</v>
+        <v>71.991</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>61.166</v>
+        <v>62.519</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>88.37</v>
+        <v>91.801</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>92.324</v>
+        <v>97.15300000000001</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>84.209</v>
+        <v>94.729</v>
       </c>
     </row>
     <row r="42">
@@ -2816,31 +2816,31 @@
         <v>52.485</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>30.536</v>
+        <v>19.719</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>30.128</v>
+        <v>21.103</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>41.071</v>
+        <v>30.395</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>39.06</v>
+        <v>35.025</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>50.858</v>
+        <v>48.302</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>29.591</v>
+        <v>28.238</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>23.584</v>
+        <v>20.153</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>29.529</v>
+        <v>24.7</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>19.788</v>
+        <v>9.268000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3613,16 +3613,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>42241</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>35508</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>31.031</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>4.998</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -3760,16 +3760,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>224693</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>202401</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>199.165</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>103.907</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
         <v>5.252</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-30.95</v>
+        <v>-18.753</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>232.078</v>
@@ -35302,7 +35302,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -35824,7 +35828,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -36774,7 +36782,11 @@
           <t>Deferred income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -37210,7 +37222,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -39264,7 +39280,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -40736,7 +40756,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -47590,7 +47614,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>
@@ -49890,7 +49918,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -52946,7 +52978,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -53116,7 +53152,11 @@
           <t>Net earnings (loss) 19</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
           <t>-</t>
@@ -53288,7 +53328,11 @@
           <t>Net earnings (loss) 19</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -61482,7 +61526,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E649" t="inlineStr">
         <is>
           <t>-</t>
@@ -62090,7 +62138,11 @@
           <t>Net earnings (loss) 21</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E656" t="inlineStr">
         <is>
           <t>-</t>
@@ -62262,7 +62314,11 @@
           <t>Net earnings (loss) 21</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E658" t="inlineStr">
         <is>
           <t>-</t>
@@ -64032,7 +64088,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D679" t="inlineStr"/>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E679" t="inlineStr">
         <is>
           <t>-</t>
@@ -66106,7 +66166,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E703" s="5" t="n">
         <v>4.322</v>
       </c>
